--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-013_休暇残日数取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-013_休暇残日数取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="12477750"/>
+    <ext cx="8572500" cy="12677775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-013 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-013 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>リクエストパラメータなし。基準日はサーバー時刻(JST)で決め、クライアントから指定できない。</t>
+          <t>リクエストパラメータなし。基準日はサーバー時刻(clock)で決め、クライアントから指定できない。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="139" customHeight="1">
+    <row r="3" ht="259" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -2387,7 +2387,11 @@
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>・確定設計変更 D1〜D10 を反映：有効な付与行の判定を expires_on &gt;= 基準日（失効日当日まで有効）に統一（findValidBalances / findConsumableForUpdate / findRestorableForUpdate / sumRemainingDays と関連記述・テスト期待値）、LeaveBalanceService#findAlertBaseRows（BAT-002 用：granted_days &gt;= 10）を追加、updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
-・BAT-002 の定義と findAlertBaseRows（Service：findAlertBaseRows(LocalDate asOf)／Repository：findAlertBaseRows(leaveTypeId, minDays, asOf) の JPQL と並び順）が一致することを確認（記載変更なし）</t>
+・BAT-002 の定義と findAlertBaseRows（Service：findAlertBaseRows(LocalDate asOf)／Repository：findAlertBaseRows(leaveTypeId, minDays, asOf) の JPQL と並び順）が一致することを確認（記載変更なし）
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・年次有給休暇の名称は LeaveType ではなく LeaveBalanceService の定数 ANNUAL_LEAVE_NAME で保持
+・grant / adjust の日数は setScale(1, RoundingMode.HALF_UP) で丸める
+・statutoryDays は 6か月未満=0日、18か月未満=10日として実装</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -4406,7 +4410,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())。パス・クエリでの userId 指定は受け付けない（本人のみ）</t>
+          <t>Controller: Long.valueOf(auth.getName())。パス・クエリでの userId 指定は受け付けない（本人のみ）</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -4748,7 +4752,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public LeaveBalanceResponse getBalances(@AuthenticationPrincipal Jwt jwt)</t>
+          <t>public LeaveBalanceResponse getBalances(Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4812,17 +4816,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン。Spring Security が @AuthenticationPrincipal で注入（sub = users.id）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4869,8 +4873,8 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Long userId = Long.valueOf(jwt.getSubject());      // トークンの sub = users.id
-return leaveBalanceService.getBalances(userId);          // 基準日 = 本日(JST)</t>
+          <t>Long userId = Long.valueOf(auth.getName());      // トークンの sub = users.id
+return leaveBalanceService.getBalances(userId);          // 基準日 = 本日(clock)</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -9477,7 +9481,7 @@
       </c>
       <c r="F295" s="7" t="inlineStr">
         <is>
-          <t>asOf 省略時は本日(JST)</t>
+          <t>asOf 省略時は本日(clock)</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9761,7 @@
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>表示（ONL-013）は本日(JST)。申請・承認（hasEnough / consume）は休暇の利用日（申請の start_date）</t>
+          <t>表示（ONL-013）は本日(clock)。申請・承認（hasEnough / consume）は休暇の利用日（申請の start_date）</t>
         </is>
       </c>
       <c r="C307" s="9" t="n"/>
